--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B362C05-E55C-447D-8389-37CB0659F623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E59342E-83B5-4E8F-B0BF-C271F9DDF25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E59342E-83B5-4E8F-B0BF-C271F9DDF25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DAE8CCB-6264-4142-A1CF-E4954E136051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,9 +304,6 @@
     <t>indesc</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
-  </si>
-  <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
@@ -335,6 +332,9 @@
   </si>
   <si>
     <t>at grid node - w90842395-400_FRA</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
   </si>
   <si>
     <t>w112342683-400_FRA</t>
@@ -887,31 +887,31 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
         <v>96</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>97</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>98</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" t="s">
         <v>88</v>
       </c>
-      <c r="G11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" t="s">
-        <v>89</v>
-      </c>
       <c r="L11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M11" t="s">
         <v>129</v>
@@ -920,12 +920,12 @@
         <v>130</v>
       </c>
       <c r="O11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -934,10 +934,10 @@
         <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
         <v>99</v>
@@ -946,10 +946,10 @@
         <v>100</v>
       </c>
       <c r="J12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M12" t="s">
         <v>109</v>
@@ -958,12 +958,12 @@
         <v>110</v>
       </c>
       <c r="O12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
         <v>101</v>
@@ -972,10 +972,10 @@
         <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
         <v>101</v>
@@ -984,10 +984,10 @@
         <v>102</v>
       </c>
       <c r="J13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s">
         <v>141</v>
@@ -996,12 +996,12 @@
         <v>142</v>
       </c>
       <c r="O13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
         <v>103</v>
@@ -1010,10 +1010,10 @@
         <v>104</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
         <v>113</v>
@@ -1022,10 +1022,10 @@
         <v>114</v>
       </c>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
         <v>137</v>
@@ -1034,12 +1034,12 @@
         <v>138</v>
       </c>
       <c r="O14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
         <v>105</v>
@@ -1048,10 +1048,10 @@
         <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
         <v>119</v>
@@ -1060,10 +1060,10 @@
         <v>120</v>
       </c>
       <c r="J15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M15" t="s">
         <v>105</v>
@@ -1072,12 +1072,12 @@
         <v>106</v>
       </c>
       <c r="O15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
         <v>107</v>
@@ -1086,10 +1086,10 @@
         <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
         <v>109</v>
@@ -1098,10 +1098,10 @@
         <v>110</v>
       </c>
       <c r="J16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M16" t="s">
         <v>119</v>
@@ -1110,12 +1110,12 @@
         <v>120</v>
       </c>
       <c r="O16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
         <v>109</v>
@@ -1124,10 +1124,10 @@
         <v>110</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
         <v>103</v>
@@ -1136,10 +1136,10 @@
         <v>104</v>
       </c>
       <c r="J17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
         <v>101</v>
@@ -1148,12 +1148,12 @@
         <v>102</v>
       </c>
       <c r="O17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
         <v>111</v>
@@ -1162,10 +1162,10 @@
         <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
         <v>105</v>
@@ -1174,10 +1174,10 @@
         <v>106</v>
       </c>
       <c r="J18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L18" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
         <v>139</v>
@@ -1186,12 +1186,12 @@
         <v>140</v>
       </c>
       <c r="O18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
         <v>113</v>
@@ -1200,10 +1200,10 @@
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s">
         <v>107</v>
@@ -1212,10 +1212,10 @@
         <v>108</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
         <v>115</v>
@@ -1224,12 +1224,12 @@
         <v>116</v>
       </c>
       <c r="O19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
         <v>115</v>
@@ -1238,10 +1238,10 @@
         <v>116</v>
       </c>
       <c r="E20" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
         <v>111</v>
@@ -1250,10 +1250,10 @@
         <v>112</v>
       </c>
       <c r="J20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
         <v>113</v>
@@ -1262,12 +1262,12 @@
         <v>114</v>
       </c>
       <c r="O20" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
         <v>117</v>
@@ -1276,10 +1276,10 @@
         <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s">
         <v>115</v>
@@ -1288,10 +1288,10 @@
         <v>116</v>
       </c>
       <c r="J21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L21" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M21" t="s">
         <v>111</v>
@@ -1300,12 +1300,12 @@
         <v>112</v>
       </c>
       <c r="O21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
         <v>119</v>
@@ -1314,10 +1314,10 @@
         <v>120</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
         <v>117</v>
@@ -1326,10 +1326,10 @@
         <v>118</v>
       </c>
       <c r="J22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M22" t="s">
         <v>107</v>
@@ -1338,12 +1338,12 @@
         <v>108</v>
       </c>
       <c r="O22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
         <v>121</v>
@@ -1352,10 +1352,10 @@
         <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
         <v>121</v>
@@ -1364,10 +1364,10 @@
         <v>122</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M23" t="s">
         <v>103</v>
@@ -1376,12 +1376,12 @@
         <v>104</v>
       </c>
       <c r="O23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
         <v>123</v>
@@ -1390,10 +1390,10 @@
         <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
         <v>123</v>
@@ -1402,10 +1402,10 @@
         <v>124</v>
       </c>
       <c r="J24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M24" t="s">
         <v>133</v>
@@ -1414,12 +1414,12 @@
         <v>134</v>
       </c>
       <c r="O24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
         <v>125</v>
@@ -1428,10 +1428,10 @@
         <v>126</v>
       </c>
       <c r="E25" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>131</v>
@@ -1440,24 +1440,24 @@
         <v>132</v>
       </c>
       <c r="J25" t="s">
+        <v>88</v>
+      </c>
+      <c r="L25" t="s">
+        <v>95</v>
+      </c>
+      <c r="M25" t="s">
+        <v>96</v>
+      </c>
+      <c r="N25" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" t="s">
         <v>89</v>
-      </c>
-      <c r="L25" t="s">
-        <v>96</v>
-      </c>
-      <c r="M25" t="s">
-        <v>97</v>
-      </c>
-      <c r="N25" t="s">
-        <v>98</v>
-      </c>
-      <c r="O25" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
         <v>127</v>
@@ -1466,10 +1466,10 @@
         <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
         <v>125</v>
@@ -1478,10 +1478,10 @@
         <v>126</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M26" t="s">
         <v>145</v>
@@ -1490,12 +1490,12 @@
         <v>146</v>
       </c>
       <c r="O26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>129</v>
@@ -1504,10 +1504,10 @@
         <v>130</v>
       </c>
       <c r="E27" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
         <v>127</v>
@@ -1516,10 +1516,10 @@
         <v>128</v>
       </c>
       <c r="J27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M27" t="s">
         <v>135</v>
@@ -1528,12 +1528,12 @@
         <v>136</v>
       </c>
       <c r="O27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
         <v>131</v>
@@ -1542,10 +1542,10 @@
         <v>132</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
         <v>129</v>
@@ -1554,10 +1554,10 @@
         <v>130</v>
       </c>
       <c r="J28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M28" t="s">
         <v>121</v>
@@ -1566,12 +1566,12 @@
         <v>122</v>
       </c>
       <c r="O28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
         <v>133</v>
@@ -1580,10 +1580,10 @@
         <v>134</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
         <v>143</v>
@@ -1592,10 +1592,10 @@
         <v>144</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M29" t="s">
         <v>143</v>
@@ -1604,12 +1604,12 @@
         <v>144</v>
       </c>
       <c r="O29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>135</v>
@@ -1618,10 +1618,10 @@
         <v>136</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s">
         <v>133</v>
@@ -1630,10 +1630,10 @@
         <v>134</v>
       </c>
       <c r="J30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M30" t="s">
         <v>99</v>
@@ -1642,12 +1642,12 @@
         <v>100</v>
       </c>
       <c r="O30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
         <v>137</v>
@@ -1656,10 +1656,10 @@
         <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
         <v>135</v>
@@ -1668,10 +1668,10 @@
         <v>136</v>
       </c>
       <c r="J31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M31" t="s">
         <v>125</v>
@@ -1680,12 +1680,12 @@
         <v>126</v>
       </c>
       <c r="O31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
         <v>139</v>
@@ -1694,10 +1694,10 @@
         <v>140</v>
       </c>
       <c r="E32" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s">
         <v>137</v>
@@ -1706,10 +1706,10 @@
         <v>138</v>
       </c>
       <c r="J32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M32" t="s">
         <v>117</v>
@@ -1718,12 +1718,12 @@
         <v>118</v>
       </c>
       <c r="O32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
         <v>141</v>
@@ -1732,10 +1732,10 @@
         <v>142</v>
       </c>
       <c r="E33" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
         <v>139</v>
@@ -1744,10 +1744,10 @@
         <v>140</v>
       </c>
       <c r="J33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M33" t="s">
         <v>123</v>
@@ -1756,12 +1756,12 @@
         <v>124</v>
       </c>
       <c r="O33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
         <v>143</v>
@@ -1770,10 +1770,10 @@
         <v>144</v>
       </c>
       <c r="E34" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s">
         <v>145</v>
@@ -1782,10 +1782,10 @@
         <v>146</v>
       </c>
       <c r="J34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L34" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M34" t="s">
         <v>131</v>
@@ -1794,12 +1794,12 @@
         <v>132</v>
       </c>
       <c r="O34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
       <c r="G35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H35" t="s">
         <v>141</v>
@@ -1808,10 +1808,10 @@
         <v>142</v>
       </c>
       <c r="J35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M35" t="s">
         <v>147</v>
@@ -1820,12 +1820,12 @@
         <v>148</v>
       </c>
       <c r="O35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
       <c r="L36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M36" t="s">
         <v>127</v>
@@ -1834,7 +1834,7 @@
         <v>128</v>
       </c>
       <c r="O36" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3066,7 +3066,7 @@
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3086,7 +3086,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
@@ -3245,7 +3245,7 @@
         <v>66</v>
       </c>
       <c r="F49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s">
         <v>65</v>
@@ -3262,7 +3262,7 @@
         <v>67</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G50" t="s">
         <v>68</v>
@@ -3290,7 +3290,7 @@
         <v>2100</v>
       </c>
       <c r="F52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">

--- a/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DAE8CCB-6264-4142-A1CF-E4954E136051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BE3C297-AEB8-4118-8121-36F025657238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
